--- a/quizzes/006_dental_histology_quiz--quizzes.xlsx
+++ b/quizzes/006_dental_histology_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cell_membranes</t>
+          <t>cell membranes</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cell_nucleus</t>
+          <t>cell nucleus</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cell_plasma</t>
+          <t>cell plasma</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cell_wall</t>
+          <t>cell wall</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cell_membrane</t>
+          <t>cell membrane</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cell_lysosomes</t>
+          <t>cell lysosomes</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cell_mitochondrion</t>
+          <t>cell mitochondrion</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cell_cytoplasm</t>
+          <t>cell cytoplasm</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cell_nuclear_membrane</t>
+          <t>cell nuclear membrane</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cell_cytoplasmic_membrane</t>
+          <t>cell cytoplasmic membrane</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dental_organ</t>
+          <t>dental organ</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tissue_connective</t>
+          <t>tissue connective</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>tissue_epithelial</t>
+          <t>tissue epithelial</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tissue_epithelial_tissue</t>
+          <t>tissue epithelial tissue</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>tissue_connective</t>
+          <t>tissue_ectodermal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>tissue_connective</t>
+          <t>tissue ectodermal</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>tissue_ectodermal</t>
+          <t>tissue_mesodermal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>tissue_ectodermal</t>
+          <t>tissue mesodermal</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>tissue_mesodermal</t>
+          <t>tissue_endodermal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tissue_mesodermal</t>
+          <t>tissue endodermal</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>tissue_endodermal</t>
+          <t>tissue_muscular</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>tissue_endodermal</t>
+          <t>tissue muscular</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tissue_classification_choices</t>
+          <t>dental_structure_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tissue_muscular</t>
+          <t>structure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tissue_muscular</t>
+          <t>structure</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>histology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>histology</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>histology</t>
+          <t>tooth</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>histology</t>
+          <t>tooth</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tooth</t>
+          <t>enamel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tooth</t>
+          <t>enamel</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>enamel</t>
+          <t>dentin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>enamel</t>
+          <t>dentin</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dentin</t>
+          <t>cementum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dentin</t>
+          <t>cementum</t>
         </is>
       </c>
     </row>
@@ -1743,46 +1743,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cementum</t>
+          <t>periodontal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cementum</t>
+          <t>periodontal</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dental_structure_choices</t>
+          <t>tooth_location_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>periodontal</t>
+          <t>tooth_location</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>periodontal</t>
+          <t>tooth location</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dental_structure_choices</t>
+          <t>tooth_location_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>tooth_surface</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>tooth surface</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tooth_location</t>
+          <t>tooth_surface_area</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tooth_location</t>
+          <t>tooth surface area</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tooth_surface</t>
+          <t>tooth_surface_location</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tooth_surface</t>
+          <t>tooth surface location</t>
         </is>
       </c>
     </row>
@@ -1828,46 +1828,46 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tooth_surface_area</t>
+          <t>tooth_location_area</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tooth_surface_area</t>
+          <t>tooth location area</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tooth_location_choices</t>
+          <t>dental_materials_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tooth_surface_location</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tooth_surface_location</t>
+          <t>materials</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tooth_location_choices</t>
+          <t>dental_materials_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tooth_location_area</t>
+          <t>materials_dental</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>tooth_location_area</t>
+          <t>materials dental</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>enamel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>enamel</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>materials_dental</t>
+          <t>dentin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>materials_dental</t>
+          <t>dentin</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>enamel</t>
+          <t>cementum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>enamel</t>
+          <t>cementum</t>
         </is>
       </c>
     </row>
@@ -1930,46 +1930,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dentin</t>
+          <t>periodontal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dentin</t>
+          <t>periodontal</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dental_materials_choices</t>
+          <t>root_canal_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>cementum</t>
+          <t>root_canal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cementum</t>
+          <t>root canal</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dental_materials_choices</t>
+          <t>root_canal_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>periodontal</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>periodontal</t>
+          <t>root</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>root_canal</t>
+          <t>canal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>root_canal</t>
+          <t>canal</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>tooth_root</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>tooth root</t>
         </is>
       </c>
     </row>
@@ -2015,46 +2015,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>tooth_canal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>canal</t>
+          <t>tooth canal</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>root_canal_choices</t>
+          <t>histology_exam_type_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>tooth_root</t>
+          <t>histology_exam_type</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>tooth_root</t>
+          <t>histology exam type</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>root_canal_choices</t>
+          <t>histology_exam_type_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tooth_canal</t>
+          <t>exam</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tooth_canal</t>
+          <t>exam</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>histology_exam_type</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>histology_exam_type</t>
+          <t>type</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>exam</t>
+          <t>histology</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>exam</t>
+          <t>histology</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>tooth_exam</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>tooth exam</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>histology</t>
+          <t>tooth_exam_type</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>histology</t>
+          <t>tooth exam type</t>
         </is>
       </c>
     </row>
@@ -2134,46 +2134,46 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>tooth_exam</t>
+          <t>tooth_exam_types</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>tooth_exam</t>
+          <t>tooth exam types</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>histology_exam_type_choices</t>
+          <t>tooth_anatomy_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>tooth_exam_type</t>
+          <t>tooth_anatomy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tooth_exam_type</t>
+          <t>tooth anatomy</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>histology_exam_type_choices</t>
+          <t>tooth_anatomy_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>tooth_exam_types</t>
+          <t>anatomy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tooth_exam_types</t>
+          <t>anatomy</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>tooth_anatomy</t>
+          <t>tooth</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>tooth_anatomy</t>
+          <t>tooth</t>
         </is>
       </c>
     </row>
@@ -2202,63 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>anatomy</t>
+          <t>anatomy_tooth</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>anatomy</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>tooth_anatomy_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>tooth</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>tooth</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>tooth_anatomy_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>anatomy_tooth</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>anatomy_tooth</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>tooth_anatomy_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>tooth_anatomy</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>tooth_anatomy</t>
+          <t>anatomy tooth</t>
         </is>
       </c>
     </row>
